--- a/proto.xlsx
+++ b/proto.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24931"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20384"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\github\work-order\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jackey\Desktop\github\work-order\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03846AE7-7276-4426-9136-E34B7E781269}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DABDFB66-268C-4C3F-8390-CC1EBBB45191}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{D2F7BAE3-AE33-4212-BD90-0DB28088F1AB}"/>
   </bookViews>
@@ -20,14 +20,6 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
   </extLst>
 </workbook>
 </file>
@@ -183,7 +175,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -750,23 +742,23 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:L26"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="26.25" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="18.25" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.5" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="18.25" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.5" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="18.25" bestFit="1" customWidth="1"/>
-    <col min="8" max="10" width="17.75" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="18.25" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="17.125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="5.5" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="9.5" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="26.21875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.21875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.44140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18.21875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.44140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18.21875" bestFit="1" customWidth="1"/>
+    <col min="8" max="10" width="17.77734375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="18.21875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="17.109375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="5.44140625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="30">
+    <row r="1" spans="1:12" ht="30.6" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -788,7 +780,7 @@
       <c r="K1" s="6"/>
       <c r="L1" s="6"/>
     </row>
-    <row r="2" spans="1:12" ht="30.75" thickBot="1">
+    <row r="2" spans="1:12" ht="31.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="10" t="s">
         <v>4</v>
       </c>
@@ -810,7 +802,7 @@
       <c r="K2" s="6"/>
       <c r="L2" s="6"/>
     </row>
-    <row r="3" spans="1:12" ht="30">
+    <row r="3" spans="1:12" ht="30.6" x14ac:dyDescent="0.3">
       <c r="A3" s="25" t="s">
         <v>8</v>
       </c>
@@ -844,7 +836,7 @@
       </c>
       <c r="L3" s="6"/>
     </row>
-    <row r="4" spans="1:12" ht="30">
+    <row r="4" spans="1:12" ht="30.6" x14ac:dyDescent="0.3">
       <c r="A4" s="10"/>
       <c r="B4" s="11"/>
       <c r="C4" s="11" t="s">
@@ -860,7 +852,7 @@
       <c r="K4" s="12"/>
       <c r="L4" s="6"/>
     </row>
-    <row r="5" spans="1:12" ht="30">
+    <row r="5" spans="1:12" ht="30.6" x14ac:dyDescent="0.3">
       <c r="A5" s="10"/>
       <c r="B5" s="11"/>
       <c r="C5" s="11" t="s">
@@ -876,7 +868,7 @@
       <c r="K5" s="12"/>
       <c r="L5" s="6"/>
     </row>
-    <row r="6" spans="1:12" ht="30">
+    <row r="6" spans="1:12" ht="30.6" x14ac:dyDescent="0.3">
       <c r="A6" s="10"/>
       <c r="B6" s="11"/>
       <c r="C6" s="11" t="s">
@@ -892,7 +884,7 @@
       <c r="K6" s="12"/>
       <c r="L6" s="6"/>
     </row>
-    <row r="7" spans="1:12" ht="30">
+    <row r="7" spans="1:12" ht="30.6" x14ac:dyDescent="0.3">
       <c r="A7" s="10"/>
       <c r="B7" s="11"/>
       <c r="C7" s="11" t="s">
@@ -908,7 +900,7 @@
       <c r="K7" s="12"/>
       <c r="L7" s="6"/>
     </row>
-    <row r="8" spans="1:12" ht="30">
+    <row r="8" spans="1:12" ht="30.6" x14ac:dyDescent="0.3">
       <c r="A8" s="10"/>
       <c r="B8" s="11"/>
       <c r="C8" s="11" t="s">
@@ -924,7 +916,7 @@
       <c r="K8" s="12"/>
       <c r="L8" s="6"/>
     </row>
-    <row r="9" spans="1:12" ht="30">
+    <row r="9" spans="1:12" ht="30.6" x14ac:dyDescent="0.3">
       <c r="A9" s="10"/>
       <c r="B9" s="11"/>
       <c r="C9" s="11" t="s">
@@ -940,7 +932,7 @@
       <c r="K9" s="12"/>
       <c r="L9" s="6"/>
     </row>
-    <row r="10" spans="1:12" ht="30">
+    <row r="10" spans="1:12" ht="30.6" x14ac:dyDescent="0.3">
       <c r="A10" s="10"/>
       <c r="B10" s="11"/>
       <c r="C10" s="11" t="s">
@@ -956,7 +948,7 @@
       <c r="K10" s="12"/>
       <c r="L10" s="6"/>
     </row>
-    <row r="11" spans="1:12" ht="30">
+    <row r="11" spans="1:12" ht="30.6" x14ac:dyDescent="0.3">
       <c r="A11" s="10"/>
       <c r="B11" s="11"/>
       <c r="C11" s="11" t="s">
@@ -972,7 +964,7 @@
       <c r="K11" s="12"/>
       <c r="L11" s="6"/>
     </row>
-    <row r="12" spans="1:12" ht="30">
+    <row r="12" spans="1:12" ht="30.6" x14ac:dyDescent="0.3">
       <c r="A12" s="10"/>
       <c r="B12" s="11"/>
       <c r="C12" s="11" t="s">
@@ -988,7 +980,7 @@
       <c r="K12" s="12"/>
       <c r="L12" s="6"/>
     </row>
-    <row r="13" spans="1:12" ht="30">
+    <row r="13" spans="1:12" ht="30.6" x14ac:dyDescent="0.3">
       <c r="A13" s="10"/>
       <c r="B13" s="11"/>
       <c r="C13" s="11" t="s">
@@ -1004,7 +996,7 @@
       <c r="K13" s="12"/>
       <c r="L13" s="6"/>
     </row>
-    <row r="14" spans="1:12" ht="30">
+    <row r="14" spans="1:12" ht="30.6" x14ac:dyDescent="0.3">
       <c r="A14" s="10"/>
       <c r="B14" s="11"/>
       <c r="C14" s="11" t="s">
@@ -1020,7 +1012,7 @@
       <c r="K14" s="12"/>
       <c r="L14" s="6"/>
     </row>
-    <row r="15" spans="1:12" ht="30">
+    <row r="15" spans="1:12" ht="30.6" x14ac:dyDescent="0.3">
       <c r="A15" s="10"/>
       <c r="B15" s="11"/>
       <c r="C15" s="11" t="s">
@@ -1036,7 +1028,7 @@
       <c r="K15" s="12"/>
       <c r="L15" s="6"/>
     </row>
-    <row r="16" spans="1:12" ht="30">
+    <row r="16" spans="1:12" ht="30.6" x14ac:dyDescent="0.3">
       <c r="A16" s="10"/>
       <c r="B16" s="11"/>
       <c r="C16" s="11" t="s">
@@ -1052,7 +1044,7 @@
       <c r="K16" s="12"/>
       <c r="L16" s="6"/>
     </row>
-    <row r="17" spans="1:12" ht="30">
+    <row r="17" spans="1:12" ht="30.6" x14ac:dyDescent="0.3">
       <c r="A17" s="10"/>
       <c r="B17" s="11"/>
       <c r="C17" s="11" t="s">
@@ -1068,7 +1060,7 @@
       <c r="K17" s="12"/>
       <c r="L17" s="6"/>
     </row>
-    <row r="18" spans="1:12" ht="30.75" thickBot="1">
+    <row r="18" spans="1:12" ht="31.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A18" s="7"/>
       <c r="B18" s="8"/>
       <c r="C18" s="8" t="s">
@@ -1084,7 +1076,7 @@
       <c r="K18" s="9"/>
       <c r="L18" s="6"/>
     </row>
-    <row r="19" spans="1:12" ht="30">
+    <row r="19" spans="1:12" ht="30.6" x14ac:dyDescent="0.3">
       <c r="A19" s="13" t="s">
         <v>18</v>
       </c>
@@ -1098,15 +1090,15 @@
       <c r="G19" s="16"/>
       <c r="H19" s="16"/>
       <c r="I19" s="16"/>
-      <c r="J19" s="14"/>
-      <c r="K19" s="13" t="s">
+      <c r="J19" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="L19" s="14" t="s">
+      <c r="K19" s="14" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="20" spans="1:12" ht="30">
+      <c r="L19" s="14"/>
+    </row>
+    <row r="20" spans="1:12" ht="30.6" x14ac:dyDescent="0.3">
       <c r="A20" s="17" t="s">
         <v>19</v>
       </c>
@@ -1130,7 +1122,7 @@
       <c r="K20" s="17"/>
       <c r="L20" s="18"/>
     </row>
-    <row r="21" spans="1:12" ht="30">
+    <row r="21" spans="1:12" ht="30.6" x14ac:dyDescent="0.3">
       <c r="A21" s="17" t="s">
         <v>20</v>
       </c>
@@ -1154,7 +1146,7 @@
       <c r="K21" s="17"/>
       <c r="L21" s="18"/>
     </row>
-    <row r="22" spans="1:12" ht="30">
+    <row r="22" spans="1:12" ht="30.6" x14ac:dyDescent="0.3">
       <c r="A22" s="17"/>
       <c r="B22" s="18"/>
       <c r="C22" s="19" t="s">
@@ -1176,7 +1168,7 @@
       <c r="K22" s="17"/>
       <c r="L22" s="18"/>
     </row>
-    <row r="23" spans="1:12" ht="30">
+    <row r="23" spans="1:12" ht="30.6" x14ac:dyDescent="0.3">
       <c r="A23" s="17"/>
       <c r="B23" s="18"/>
       <c r="C23" s="19" t="s">
@@ -1196,7 +1188,7 @@
       <c r="K23" s="17"/>
       <c r="L23" s="18"/>
     </row>
-    <row r="24" spans="1:12" ht="30.75" thickBot="1">
+    <row r="24" spans="1:12" ht="31.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A24" s="21"/>
       <c r="B24" s="22"/>
       <c r="C24" s="23" t="s">
@@ -1216,7 +1208,7 @@
       <c r="K24" s="21"/>
       <c r="L24" s="22"/>
     </row>
-    <row r="26" spans="1:12">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
       <c r="C26" s="1"/>
     </row>
   </sheetData>
